--- a/data/trans_orig/P15E_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57904</t>
+          <t>57325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68995</t>
+          <t>68831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53953</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64997</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87822</t>
+          <t>88618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42826</t>
+          <t>42915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>52667</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>47060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53017</t>
+          <t>57190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57325</t>
+          <t>61510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>73605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26696</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53408</t>
+          <t>58377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89296</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73293</t>
+          <t>81289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88618</t>
+          <t>97038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28692</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42915</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
